--- a/Doc/导出配置/Level.xlsx
+++ b/Doc/导出配置/Level.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\github\PokerGame\Doc\导出配置\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF879435-6A91-47B8-A1FD-D830FAC51DCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9318F-1B73-4172-8F4D-1C282823D8AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cfg_Level" sheetId="1" r:id="rId1"/>
     <sheet name="Cfg_LevelEndCondition" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -28,10 +28,10 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{84B7F796-A7C8-4CF0-A1FC-70DDFA3FD8C9}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{DB478F70-CFE1-4C61-8AD6-39E7325B7870}">
       <text>
         <r>
           <rPr>
@@ -42,22 +42,18 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+id
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false</t>
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{A60F1552-DA93-4116-9C23-BD90168FDA16}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{276264D1-49F4-48FC-BE87-3494E1193736}">
       <text>
         <r>
           <rPr>
@@ -68,22 +64,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+monsterList
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false
+【内容格式】：
+数据名.方法名1[参数1,参数2……].方法名2[参数1,参数2……].…….方法名[Key1=Value1,Key2=Value2]……
+其中参数值如果为默认值可省略，具体方法对应的参数序号和默认值见系统_参数设置的数据表处理方法配置
+如果表头配置的转换关键字配置了方法，此处可只配置数据配置</t>
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{7B2CF404-01B7-4BF3-8977-333AB67F470E}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{BEABC0EE-F13D-4C59-9393-5DCAA0A8AF95}">
       <text>
         <r>
           <rPr>
@@ -94,22 +90,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+successCondition
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false
+【内容格式】：
+数据名.方法名1[参数1,参数2……].方法名2[参数1,参数2……].…….方法名[Key1=Value1,Key2=Value2]……
+其中参数值如果为默认值可省略，具体方法对应的参数序号和默认值见系统_参数设置的数据表处理方法配置
+如果表头配置的转换关键字配置了方法，此处可只配置数据配置</t>
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{3E35A430-7B87-4F98-89DD-49F7036689D5}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{CBA5A70D-4022-4E0D-95A2-3D496C9E9D80}">
       <text>
         <r>
           <rPr>
@@ -120,22 +116,22 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+faildCondition
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false
+【内容格式】：
+数据名.方法名1[参数1,参数2……].方法名2[参数1,参数2……].…….方法名[Key1=Value1,Key2=Value2]……
+其中参数值如果为默认值可省略，具体方法对应的参数序号和默认值见系统_参数设置的数据表处理方法配置
+如果表头配置的转换关键字配置了方法，此处可只配置数据配置</t>
         </r>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{DEF0749E-6067-439E-9CA1-6432F57F78C8}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{9370C66E-8E94-4320-B063-6E8860A7872E}">
       <text>
         <r>
           <rPr>
@@ -146,22 +142,20 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-</t>
+          <t>【字段名】：
+firstKillReward
+【表头】：
+c
+【数据类型】：
+字符
+【为空是否导出】：
+false
+【转换目标字段】
+：Random表的ID字段</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{B9D87F9F-3848-4167-9044-E2DEE38967ED}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{4AD1D0C5-88DC-4FAD-9FAC-DC3BEBF73877}">
       <text>
         <r>
           <rPr>
@@ -192,10 +186,10 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>admin</author>
+    <author>毛俭铭</author>
   </authors>
   <commentList>
-    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{30E48212-09D7-4AD0-BD22-478B76488E50}">
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{0A2858EC-D0CF-431B-8395-AC186AA09713}">
       <text>
         <r>
           <rPr>
@@ -217,7 +211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{B919FFB7-45D7-4A5A-B50B-AAB2F48A597A}">
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{C2BDB860-C88D-4176-85BE-7DB99E884E76}">
       <text>
         <r>
           <rPr>
@@ -244,7 +238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{A1F77750-CB18-4446-B5C4-065A87C5AA82}">
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{49B7AF49-0D9E-4200-8B26-8159C9F58E80}">
       <text>
         <r>
           <rPr>
@@ -271,7 +265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{910A10DF-0EDB-4DB5-99AC-DC1A56E82F1F}">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{127B1D3D-55FE-4C88-9FCC-61E411CA5DB1}">
       <text>
         <r>
           <rPr>
@@ -353,7 +347,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -373,13 +367,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -974,13 +961,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.44140625" style="1" bestFit="1" customWidth="1"/>
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1053,7 +1040,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F6A5F3-7B96-45E3-B21A-BF6DA3EE9C64}">
   <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
     <col min="3" max="3" width="11" style="1" bestFit="1" customWidth="1"/>
